--- a/03-entregables/13-respuesta-observaciones-validacion-interna/RESPUESTA-OBSERVACIONES-validacion-interna.xlsx
+++ b/03-entregables/13-respuesta-observaciones-validacion-interna/RESPUESTA-OBSERVACIONES-validacion-interna.xlsx
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>§5 trabajo futuro: agente en el router perimetral pfSense, complementario a los agentes de host. No se prototipó.</t>
+          <t>§5 trabajo futuro: integrar la respuesta con el equipo perimetral de la red para que una detección genere automáticamente la regla en él, complementando a los agentes de host. Queda como trabajo futuro, sin atarlo a un producto concreto; no se prototipó.</t>
         </is>
       </c>
       <c r="K17" s="7" t="inlineStr">
